--- a/wwwroot/Templates/Template_Participants.xlsx
+++ b/wwwroot/Templates/Template_Participants.xlsx
@@ -430,7 +430,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" style="1" min="1" max="1"/>
   </cols>
@@ -453,8 +453,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
@@ -466,9 +466,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -500,7 +498,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. Maximum 500 rows per upload. Participants are limited by the Quota entered on the form.</t>
+          <t>5. Maximum 500 rows per upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6. Create Event: participants are limited by the Quota entered on the form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7. Realization: uploaded employees are added as walk-in participants and marked Present (can be changed before saving).</t>
         </is>
       </c>
     </row>
